--- a/Result/profitability/3211.xlsx
+++ b/Result/profitability/3211.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>2.32</v>
       </c>
       <c r="M2" t="n">
-        <v>2.59</v>
+        <v>1.965</v>
       </c>
       <c r="N2" t="n">
-        <v>15.37125</v>
+        <v>15.76125</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.56</v>
       </c>
       <c r="M3" t="n">
-        <v>2.24</v>
+        <v>2.2925</v>
       </c>
       <c r="N3" t="n">
-        <v>15.92125</v>
+        <v>16.2</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>4.09</v>
       </c>
       <c r="M4" t="n">
-        <v>2.63375</v>
+        <v>2.67</v>
       </c>
       <c r="N4" t="n">
-        <v>16.16</v>
+        <v>15.9025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>2.69375</v>
+        <v>2.3775</v>
       </c>
       <c r="N5" t="n">
-        <v>15.49</v>
+        <v>15.565</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>2.385</v>
+        <v>2.36</v>
       </c>
       <c r="N6" t="n">
-        <v>14.8875</v>
+        <v>14.60125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.61</v>
       </c>
       <c r="M7" t="n">
-        <v>2.51625</v>
+        <v>2.37</v>
       </c>
       <c r="N7" t="n">
-        <v>14.76375</v>
+        <v>13.9775</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.58</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5225</v>
+        <v>2.43625</v>
       </c>
       <c r="N8" t="n">
-        <v>14.1475</v>
+        <v>13.375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3491</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3008</v>
+      </c>
+      <c r="E75" t="n">
+        <v>483</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>227</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>242</v>
+      </c>
+      <c r="K75" t="n">
+        <v>207</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.20875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6899999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3365853658536584</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.180000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.308537194208687</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6503856041131105</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04528301886792452</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
